--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Separazione e divorzio.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Separazione e divorzio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="110">
   <si>
     <r>
       <t xml:space="preserve">
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>…voglio ricevere una conferma quando l’appuntamento viene confermato dall’ente.</t>
+  </si>
+  <si>
+    <t>…voglio ricevere una conferma quando l’appuntamento viene confermato dall’ente.\</t>
   </si>
   <si>
     <t>…voglio ricevere un promemoria del mio appuntamento.</t>
@@ -1241,7 +1244,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -1312,14 +1315,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t>✨ Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi della scadenza tramite notifica push.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promemoria automatici — Messaggi Premium
-Impostando il messaggio di Avviso di pagamento come Messaggio Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, non è necessario inviare il seguente messaggio di promemoria.
-Gli utenti che hanno dato il loro consenso, infatti, riceveranno automaticamente una notifica push sui loro dispositivi all’avvicinarsi della scadenza.</t>
   </si>
   <si>
     <t xml:space="preserve">Mancato pagamento
@@ -1938,173 +1933,173 @@
         <v>62</v>
       </c>
       <c r="D2" s="34" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E2" s="34" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F2" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="I2" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="34" t="s">
-        <v>65</v>
-      </c>
-      <c r="H2" s="34" t="s">
-        <v>65</v>
-      </c>
-      <c r="I2" s="34" t="s">
-        <v>66</v>
-      </c>
-      <c r="J2" s="34" t="s">
-        <v>63</v>
-      </c>
       <c r="K2" s="34" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="32" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F3" s="34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G3" s="34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H3" s="34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I3" s="34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J3" s="34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K3" s="34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E4" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="H4" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="I4" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="J4" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="G4" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="H4" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="I4" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="J4" s="33" t="s">
-        <v>73</v>
-      </c>
       <c r="K4" s="33" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="32" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G5" s="34" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H5" s="34" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I5" s="34" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J5" s="34" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K5" s="34" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F6" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="G6" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="H6" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="I6" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="G6" s="34" t="s">
+      <c r="J6" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="H6" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="I6" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="J6" s="34" t="s">
-        <v>90</v>
-      </c>
       <c r="K6" s="34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>59</v>
@@ -2139,112 +2134,112 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I8" s="34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J8" s="34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K8" s="34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H9" s="34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I9" s="34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J9" s="34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K9" s="34" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E10" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="F10" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="G10" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="H10" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="I10" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="F10" s="34" t="s">
+      <c r="J10" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="G10" s="34" t="s">
-        <v>105</v>
-      </c>
-      <c r="H10" s="34" t="s">
-        <v>105</v>
-      </c>
-      <c r="I10" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="J10" s="34" t="s">
-        <v>104</v>
-      </c>
       <c r="K10" s="34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>59</v>
@@ -2259,13 +2254,13 @@
         <v>59</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>108</v>
+        <v>59</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="H11" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I11" s="34" t="s">
         <v>59</v>
